--- a/人员信息模板.xlsx
+++ b/人员信息模板.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="26">
   <si>
     <t>姓名</t>
   </si>
@@ -38,6 +38,9 @@
     <t>体检编码</t>
   </si>
   <si>
+    <t>性别</t>
+  </si>
+  <si>
     <t>身高</t>
   </si>
   <si>
@@ -69,6 +72,9 @@
   </si>
   <si>
     <t>202607080007</t>
+  </si>
+  <si>
+    <t>男</t>
   </si>
   <si>
     <t>2026-07-08</t>
@@ -1065,17 +1071,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="4"/>
   <cols>
     <col min="2" max="2" width="20.7142857142857" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="9" max="9" width="12.7857142857143" customWidth="1"/>
-    <col min="10" max="10" width="10.6428571428571" customWidth="1"/>
-    <col min="11" max="11" width="12.7857142857143"/>
+    <col min="3" max="4" width="14" customWidth="1"/>
+    <col min="10" max="10" width="12.7857142857143" customWidth="1"/>
+    <col min="11" max="11" width="10.6428571428571" customWidth="1"/>
+    <col min="12" max="12" width="12.7857142857143"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:12">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1109,115 +1115,127 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="2" ht="17" spans="1:11">
+    <row r="2" ht="17" spans="1:12">
       <c r="A2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2">
+        <v>14</v>
+      </c>
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2">
         <v>160</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>60</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>22.62</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>121</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>85</v>
       </c>
-      <c r="I2">
+      <c r="J2">
         <v>17381240178</v>
       </c>
-      <c r="J2" s="2" t="s">
-        <v>14</v>
-      </c>
       <c r="K2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
         <v>15</v>
       </c>
+      <c r="E3">
+        <v>168</v>
+      </c>
+      <c r="F3">
+        <v>60</v>
+      </c>
+      <c r="G3">
+        <v>22.56</v>
+      </c>
+      <c r="H3">
+        <v>122</v>
+      </c>
+      <c r="I3">
+        <v>86</v>
+      </c>
+      <c r="J3">
+        <v>18909036281</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="3" spans="1:11">
-      <c r="A3" t="s">
+    <row r="4" spans="1:12">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4">
+        <v>168</v>
+      </c>
+      <c r="F4">
+        <v>62.5</v>
+      </c>
+      <c r="G4">
+        <v>22.58</v>
+      </c>
+      <c r="H4">
+        <v>118</v>
+      </c>
+      <c r="I4">
+        <v>83</v>
+      </c>
+      <c r="J4">
+        <v>15828157042</v>
+      </c>
+      <c r="K4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3">
-        <v>168</v>
-      </c>
-      <c r="E3">
-        <v>60</v>
-      </c>
-      <c r="F3">
-        <v>22.56</v>
-      </c>
-      <c r="G3">
-        <v>122</v>
-      </c>
-      <c r="H3">
-        <v>86</v>
-      </c>
-      <c r="I3">
-        <v>18909036281</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>19</v>
+      <c r="L4" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
-      <c r="A4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4">
-        <v>168</v>
-      </c>
-      <c r="E4">
-        <v>62.5</v>
-      </c>
-      <c r="F4">
-        <v>22.58</v>
-      </c>
-      <c r="G4">
-        <v>118</v>
-      </c>
-      <c r="H4">
-        <v>83</v>
-      </c>
-      <c r="I4">
-        <v>15828157042</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="10:11">
-      <c r="J5" s="2"/>
+    <row r="5" spans="11:12">
       <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/人员信息模板.xlsx
+++ b/人员信息模板.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="27">
   <si>
     <t>姓名</t>
   </si>
@@ -102,6 +102,9 @@
   </si>
   <si>
     <t>202607080010</t>
+  </si>
+  <si>
+    <t>女</t>
   </si>
   <si>
     <t>09:56</t>
@@ -1206,7 +1209,7 @@
         <v>24</v>
       </c>
       <c r="D4" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E4">
         <v>168</v>
@@ -1230,7 +1233,7 @@
         <v>16</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="11:12">
